--- a/storage/app/pdfs/blending_europe_components.xlsx
+++ b/storage/app/pdfs/blending_europe_components.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://faro90mx-my.sharepoint.com/personal/rfavela_hcx_mx/Documents/F90/Operacion/Proyectos/Proyectos en curso/US Grains 013 (Analisis Global)/Europa/1. Informacion Europa/2. Blending/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rodrigofavela/Desktop/Update Blending EIH/BLENDING/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="13_ncr:1_{B3F9FA0F-82D6-0242-84D8-0231938CF8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EEB4E68-33E3-6843-9FCD-664123A437BD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F76FB16-0BD3-4F4A-A116-59CE04495F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1600" yWindow="880" windowWidth="23260" windowHeight="12460" tabRatio="853" firstSheet="18" activeTab="28" xr2:uid="{AD60D5F5-4EC3-4F16-A51A-8F435208B142}"/>
+    <workbookView xWindow="1600" yWindow="880" windowWidth="23260" windowHeight="12460" tabRatio="853" activeTab="1" xr2:uid="{AD60D5F5-4EC3-4F16-A51A-8F435208B142}"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="7" r:id="rId1"/>
@@ -550,11 +550,11 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -979,12 +979,12 @@
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="32" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A6" s="31"/>
+      <c r="A6" s="32"/>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
@@ -1180,7 +1180,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="27" style="8" bestFit="1" customWidth="1"/>
@@ -1207,22 +1207,22 @@
     </row>
     <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -2134,40 +2134,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.1819203257699602</v>
+        <v>1.9789501713451367</v>
       </c>
       <c r="C24" s="15">
-        <v>2.1818639465083289</v>
+        <v>1.9788937920835055</v>
       </c>
       <c r="D24" s="15">
-        <v>2.1818701885910707</v>
+        <v>1.9789000341662473</v>
       </c>
       <c r="E24" s="15">
-        <v>2.1818972210068419</v>
+        <v>1.9789270665820184</v>
       </c>
       <c r="F24" s="15">
-        <v>2.1819186555679573</v>
+        <v>1.9789485011431338</v>
       </c>
       <c r="G24" s="15">
-        <v>2.1818967592061811</v>
+        <v>1.9789266047813576</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2935213458055386</v>
+        <v>2.0905511913807153</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1561753585250036</v>
+        <v>1.9532052041001802</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0562433314048283</v>
+        <v>1.8532731769800048</v>
       </c>
       <c r="L24" s="27">
-        <v>1.9406142648483318</v>
+        <v>1.7376441104235083</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8946475125038311</v>
+        <v>1.6916773580790077</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8422742429849814</v>
+        <v>1.639304088560158</v>
       </c>
       <c r="Q24" s="28"/>
       <c r="R24" s="18"/>
@@ -2227,22 +2227,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -3117,40 +3117,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.3135780200223368</v>
+        <v>2.1106078655975136</v>
       </c>
       <c r="C48" s="15">
-        <v>2.3135781106265068</v>
+        <v>2.1106079562016831</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3135781106889417</v>
+        <v>2.1106079562641185</v>
       </c>
       <c r="E48" s="15">
-        <v>2.3135153584728227</v>
+        <v>2.1105452040479991</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3135781107040359</v>
+        <v>2.1106079562792122</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3135781107004885</v>
+        <v>2.1106079562756648</v>
       </c>
       <c r="I48" s="27">
-        <v>2.3135781081460154</v>
+        <v>2.1106079537211917</v>
       </c>
       <c r="J48" s="27">
-        <v>2.1967640241950699</v>
+        <v>1.9937938697702464</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1277866279398716</v>
+        <v>1.9248164735150481</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0560232157481169</v>
+        <v>1.8530530613232934</v>
       </c>
       <c r="M48" s="27">
-        <v>1.9913718047335693</v>
+        <v>1.7884016503087459</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9411172040494982</v>
+        <v>1.7381470496246747</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -3193,6 +3193,51 @@
       <c r="N49" s="26">
         <v>98.000000252691251</v>
       </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3213,7 +3258,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W52"/>
+  <dimension ref="A1:W54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="27" style="8" bestFit="1" customWidth="1"/>
@@ -3240,22 +3285,22 @@
     </row>
     <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -4167,40 +4212,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.2116978779540144</v>
+        <v>2.0087277235291907</v>
       </c>
       <c r="C24" s="15">
-        <v>2.2116978818591875</v>
+        <v>2.0087277274343638</v>
       </c>
       <c r="D24" s="15">
-        <v>2.2116978770068911</v>
+        <v>2.0087277225820674</v>
       </c>
       <c r="E24" s="15">
-        <v>2.211697876557901</v>
+        <v>2.0087277221330773</v>
       </c>
       <c r="F24" s="15">
-        <v>2.2116978789171911</v>
+        <v>2.0087277244923678</v>
       </c>
       <c r="G24" s="15">
-        <v>2.2116978764249042</v>
+        <v>2.0087277220000805</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2681139700936508</v>
+        <v>2.0651438156688275</v>
       </c>
       <c r="J24" s="27">
-        <v>2.157512032301625</v>
+        <v>1.9545418778768016</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0785750014652855</v>
+        <v>1.875604847040462</v>
       </c>
       <c r="L24" s="27">
-        <v>1.9955761583970222</v>
+        <v>1.7926060039721987</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8815000578811425</v>
+        <v>1.678529903456319</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8101392494065784</v>
+        <v>1.607169094981755</v>
       </c>
       <c r="Q24" s="28"/>
       <c r="R24" s="18"/>
@@ -4260,22 +4305,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -5150,40 +5195,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.3461620153406946</v>
+        <v>2.1431918609158709</v>
       </c>
       <c r="C48" s="15">
-        <v>2.3461620104326437</v>
+        <v>2.14319185600782</v>
       </c>
       <c r="D48" s="15">
-        <v>2.346161999367729</v>
+        <v>2.1431918449429057</v>
       </c>
       <c r="E48" s="15">
-        <v>2.3461620107909202</v>
+        <v>2.143191856366097</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3461620117629529</v>
+        <v>2.1431918573381292</v>
       </c>
       <c r="G48" s="15">
-        <v>2.346162000468476</v>
+        <v>2.1431918460436528</v>
       </c>
       <c r="I48" s="27">
-        <v>2.3461620113663719</v>
+        <v>2.1431918569415487</v>
       </c>
       <c r="J48" s="27">
-        <v>2.2216151023347819</v>
+        <v>2.0186449479099586</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1507845285652345</v>
+        <v>1.947814374140411</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0755590883241912</v>
+        <v>1.8725889338993678</v>
       </c>
       <c r="M48" s="27">
-        <v>1.9980246983411998</v>
+        <v>1.7950545439163763</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9234862356427109</v>
+        <v>1.7205160812178875</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -5274,6 +5319,36 @@
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5321,22 +5396,22 @@
     </row>
     <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -6248,40 +6323,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.208918035493463</v>
+        <v>2.0059478810686393</v>
       </c>
       <c r="C24" s="15">
-        <v>2.2089180443743959</v>
+        <v>2.0059478899495726</v>
       </c>
       <c r="D24" s="15">
-        <v>2.2089180085476507</v>
+        <v>2.0059478541228275</v>
       </c>
       <c r="E24" s="15">
-        <v>2.2089180171439557</v>
+        <v>2.0059478627191325</v>
       </c>
       <c r="F24" s="15">
-        <v>2.2089180274562565</v>
+        <v>2.0059478730314328</v>
       </c>
       <c r="G24" s="15">
-        <v>2.2089180286230832</v>
+        <v>2.0059478741982595</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2718885266136519</v>
+        <v>2.0689183721888282</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1440460770614469</v>
+        <v>1.9410759226366234</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0826875216639755</v>
+        <v>1.8797173672391521</v>
       </c>
       <c r="L24" s="27">
-        <v>2.0023953751351882</v>
+        <v>1.7994252207103647</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8797001402794935</v>
+        <v>1.67672998585467</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8144825697117761</v>
+        <v>1.6115124152869527</v>
       </c>
       <c r="Q24" s="28"/>
       <c r="R24" s="18"/>
@@ -6341,22 +6416,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -7231,40 +7306,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.3472323491829101</v>
+        <v>2.1442621947580864</v>
       </c>
       <c r="C48" s="15">
-        <v>2.3472323490799218</v>
+        <v>2.1442621946550986</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3472323488495976</v>
+        <v>2.1442621944247744</v>
       </c>
       <c r="E48" s="15">
-        <v>2.3472323491831664</v>
+        <v>2.1442621947583431</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3472323491344831</v>
+        <v>2.1442621947096594</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3472323491832445</v>
+        <v>2.1442621947584213</v>
       </c>
       <c r="I48" s="27">
-        <v>2.3472323492958109</v>
+        <v>2.1442621948709872</v>
       </c>
       <c r="J48" s="27">
-        <v>2.2180673646194169</v>
+        <v>2.0150972101945932</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1458463528413265</v>
+        <v>1.9428761984165031</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0691968976365613</v>
+        <v>1.8662267432117379</v>
       </c>
       <c r="M48" s="27">
-        <v>1.9917833968801764</v>
+        <v>1.7888132424553529</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9248691808624778</v>
+        <v>1.7218990264376544</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -7803,22 +7878,22 @@
     </row>
     <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
       <c r="O4" s="1"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
@@ -8750,40 +8825,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.1955181897931744</v>
+        <v>1.9925480353683509</v>
       </c>
       <c r="C24" s="15">
-        <v>2.1955181797783432</v>
+        <v>1.9925480253535197</v>
       </c>
       <c r="D24" s="15">
-        <v>2.195518183346528</v>
+        <v>1.9925480289217046</v>
       </c>
       <c r="E24" s="15">
-        <v>2.1955181804724662</v>
+        <v>1.9925480260476427</v>
       </c>
       <c r="F24" s="15">
-        <v>2.1955181705503612</v>
+        <v>1.9925480161255378</v>
       </c>
       <c r="G24" s="15">
-        <v>2.1955181678043809</v>
+        <v>1.9925480133795574</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2581548789250272</v>
+        <v>2.0551847245002035</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1350196881211354</v>
+        <v>1.9320495336963119</v>
       </c>
       <c r="K24" s="27">
-        <v>2.068864015536386</v>
+        <v>1.8658938611115625</v>
       </c>
       <c r="L24" s="27">
-        <v>2.0020712088749115</v>
+        <v>1.7991010544500881</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8810028706547974</v>
+        <v>1.678032716229974</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8449689707113528</v>
+        <v>1.6419988162865293</v>
       </c>
       <c r="O24" s="1"/>
       <c r="Q24" s="28"/>
@@ -8851,22 +8926,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
@@ -9751,40 +9826,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.3299823297159019</v>
+        <v>2.1270121752910782</v>
       </c>
       <c r="C48" s="15">
-        <v>2.3299823287878332</v>
+        <v>2.1270121743630099</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3299823285464094</v>
+        <v>2.1270121741215862</v>
       </c>
       <c r="E48" s="15">
-        <v>2.3299823295618283</v>
+        <v>2.127012175137005</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3299823285862202</v>
+        <v>2.127012174161397</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3299823292202411</v>
+        <v>2.1270121747954178</v>
       </c>
       <c r="I48" s="27">
-        <v>2.3299823296196092</v>
+        <v>2.1270121751947855</v>
       </c>
       <c r="J48" s="27">
-        <v>2.2037861655744773</v>
+        <v>2.000816011149654</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1317786520893143</v>
+        <v>1.9288084976644908</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0570225631223087</v>
+        <v>1.8540524086974852</v>
       </c>
       <c r="M48" s="27">
-        <v>1.9799214983492786</v>
+        <v>1.7769513439244551</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9239136151291363</v>
+        <v>1.7209434607043128</v>
       </c>
       <c r="O48" s="1"/>
     </row>
@@ -11169,22 +11244,22 @@
     </row>
     <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
       <c r="O4" s="1"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
@@ -12116,40 +12191,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.1977396446600417</v>
+        <v>1.9947694902352182</v>
       </c>
       <c r="C24" s="15">
-        <v>2.1977396446473692</v>
+        <v>1.9947694902225457</v>
       </c>
       <c r="D24" s="15">
-        <v>2.1977396446025095</v>
+        <v>1.994769490177686</v>
       </c>
       <c r="E24" s="15">
-        <v>2.1977396446538826</v>
+        <v>1.9947694902290591</v>
       </c>
       <c r="F24" s="15">
-        <v>2.1977396446046371</v>
+        <v>1.9947694901798136</v>
       </c>
       <c r="G24" s="15">
-        <v>2.1977396446562505</v>
+        <v>1.994769490231427</v>
       </c>
       <c r="I24" s="27">
-        <v>2.296860523101008</v>
+        <v>2.0938903686761847</v>
       </c>
       <c r="J24" s="27">
-        <v>2.168102025206835</v>
+        <v>1.9651318707820116</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0992689165720115</v>
+        <v>1.8962987621471881</v>
       </c>
       <c r="L24" s="27">
-        <v>2.0205634713110689</v>
+        <v>1.8175933168862455</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8781566464036323</v>
+        <v>1.6751864919788089</v>
       </c>
       <c r="N24" s="27">
-        <v>1.84057103110989</v>
+        <v>1.6376008766850665</v>
       </c>
       <c r="O24" s="1"/>
       <c r="Q24" s="28"/>
@@ -12217,22 +12292,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
@@ -13117,40 +13192,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.3289583246692329</v>
+        <v>2.1259881702444092</v>
       </c>
       <c r="C48" s="15">
-        <v>2.3289583205056879</v>
+        <v>2.1259881660808642</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3289602415741468</v>
+        <v>2.1259900871493231</v>
       </c>
       <c r="E48" s="15">
-        <v>2.3289583120738584</v>
+        <v>2.1259881576490347</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3289583223916734</v>
+        <v>2.1259881679668498</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3289583202542152</v>
+        <v>2.1259881658293915</v>
       </c>
       <c r="I48" s="27">
-        <v>2.3289583291772318</v>
+        <v>2.1259881747524085</v>
       </c>
       <c r="J48" s="27">
-        <v>2.208041753959407</v>
+        <v>2.0050715995345838</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1389047056711337</v>
+        <v>1.9359345512463102</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0638260329377935</v>
+        <v>1.8608558785129701</v>
       </c>
       <c r="M48" s="27">
-        <v>1.9867219056356122</v>
+        <v>1.7837517512107888</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9227753695896688</v>
+        <v>1.7198052151648453</v>
       </c>
       <c r="O48" s="1"/>
     </row>
@@ -13215,53 +13290,14 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
-      <c r="N51" s="1"/>
       <c r="O51" s="1"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-      <c r="N52" s="1"/>
       <c r="O52" s="1"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
-      <c r="M53" s="1"/>
-      <c r="N53" s="1"/>
       <c r="O53" s="1"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.15">
@@ -13329,22 +13365,22 @@
     </row>
     <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -14256,40 +14292,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.3012696138746342</v>
+        <v>2.0982994594498106</v>
       </c>
       <c r="C24" s="15">
-        <v>2.3012696138746316</v>
+        <v>2.0982994594498079</v>
       </c>
       <c r="D24" s="15">
-        <v>2.3012696138746391</v>
+        <v>2.0982994594498159</v>
       </c>
       <c r="E24" s="15">
-        <v>2.3012696138746187</v>
+        <v>2.0982994594497955</v>
       </c>
       <c r="F24" s="15">
-        <v>2.3012696138746565</v>
+        <v>2.0982994594498328</v>
       </c>
       <c r="G24" s="15">
-        <v>2.3012696138747009</v>
+        <v>2.0982994594498772</v>
       </c>
       <c r="I24" s="27">
-        <v>2.3166256076660452</v>
+        <v>2.1136554532412219</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1871391231293615</v>
+        <v>1.9841689687045381</v>
       </c>
       <c r="K24" s="27">
-        <v>2.1049583993618635</v>
+        <v>1.90198824493704</v>
       </c>
       <c r="L24" s="27">
-        <v>1.9955214359084816</v>
+        <v>1.7925512814836582</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8860101684385233</v>
+        <v>1.6830400140136998</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8207968279973312</v>
+        <v>1.6178266735725078</v>
       </c>
       <c r="Q24" s="28"/>
       <c r="R24" s="18"/>
@@ -14349,22 +14385,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -15239,40 +15275,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.4250613440527409</v>
+        <v>2.2220911896279176</v>
       </c>
       <c r="C48" s="15">
-        <v>2.4250638784350689</v>
+        <v>2.2220937240102456</v>
       </c>
       <c r="D48" s="15">
-        <v>2.4250618159354027</v>
+        <v>2.2220916615105795</v>
       </c>
       <c r="E48" s="15">
-        <v>2.4250634042193076</v>
+        <v>2.2220932497944839</v>
       </c>
       <c r="F48" s="15">
-        <v>2.4250613438419126</v>
+        <v>2.2220911894170889</v>
       </c>
       <c r="G48" s="15">
-        <v>2.4250622985764885</v>
+        <v>2.2220921441516648</v>
       </c>
       <c r="I48" s="27">
-        <v>2.4395170472119352</v>
+        <v>2.2365468927871115</v>
       </c>
       <c r="J48" s="27">
-        <v>2.3166996248095315</v>
+        <v>2.1137294703847083</v>
       </c>
       <c r="K48" s="27">
-        <v>2.2397857028474437</v>
+        <v>2.03681554842262</v>
       </c>
       <c r="L48" s="27">
-        <v>2.1571036682962683</v>
+        <v>1.9541335138714448</v>
       </c>
       <c r="M48" s="27">
-        <v>2.0617341526156601</v>
+        <v>1.8587639981908366</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9666221559777921</v>
+        <v>1.7636520015529686</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -15334,35 +15370,9 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
-      <c r="N51" s="1"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-      <c r="N52" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -15411,22 +15421,22 @@
     </row>
     <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
       <c r="O4" s="1"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
@@ -16358,40 +16368,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.1768592907937854</v>
+        <v>1.9738891363689619</v>
       </c>
       <c r="C24" s="15">
-        <v>2.1768593164086258</v>
+        <v>1.9738891619838024</v>
       </c>
       <c r="D24" s="15">
-        <v>2.1768593161513157</v>
+        <v>1.9738891617264922</v>
       </c>
       <c r="E24" s="15">
-        <v>2.1768593212240575</v>
+        <v>1.973889166799234</v>
       </c>
       <c r="F24" s="15">
-        <v>2.1768593146978259</v>
+        <v>1.9738891602730024</v>
       </c>
       <c r="G24" s="15">
-        <v>2.1768593173456106</v>
+        <v>1.9738891629207871</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2576200331476071</v>
+        <v>2.0546498787227838</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1454682198500095</v>
+        <v>1.942498065425186</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0624410488075671</v>
+        <v>1.8594708943827436</v>
       </c>
       <c r="L24" s="27">
-        <v>1.9861009541056691</v>
+        <v>1.7831307996808456</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8907122686344418</v>
+        <v>1.6877421142096183</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8174047467626357</v>
+        <v>1.6144345923378123</v>
       </c>
       <c r="O24" s="1"/>
       <c r="Q24" s="28"/>
@@ -16459,22 +16469,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
@@ -17359,40 +17369,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.3071184896556325</v>
+        <v>2.1041483352308088</v>
       </c>
       <c r="C48" s="15">
-        <v>2.3071184880923048</v>
+        <v>2.1041483336674816</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3071184861235312</v>
+        <v>2.104148331698708</v>
       </c>
       <c r="E48" s="15">
-        <v>2.3071184877890585</v>
+        <v>2.1041483333642352</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3071184853928841</v>
+        <v>2.1041483309680604</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3071184874711985</v>
+        <v>2.1041483330463748</v>
       </c>
       <c r="I48" s="27">
-        <v>2.3071180321695755</v>
+        <v>2.1041478777447518</v>
       </c>
       <c r="J48" s="27">
-        <v>2.1881137128570436</v>
+        <v>1.9851435584322201</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1191362516859473</v>
+        <v>1.9161660972611239</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0488512671525387</v>
+        <v>1.8458811127277153</v>
       </c>
       <c r="M48" s="27">
-        <v>1.9786635263969268</v>
+        <v>1.7756933719721033</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9259415458966467</v>
+        <v>1.7229713914718232</v>
       </c>
       <c r="O48" s="1"/>
     </row>
@@ -17593,7 +17603,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W51"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="30.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -17621,22 +17631,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
       <c r="O4" s="12"/>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.2">
@@ -18577,40 +18587,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.1619203257699602</v>
+        <v>1.9589501713451367</v>
       </c>
       <c r="C24" s="15">
-        <v>2.1618639465083289</v>
+        <v>1.9588937920835054</v>
       </c>
       <c r="D24" s="15">
-        <v>2.1618701885910707</v>
+        <v>1.9589000341662473</v>
       </c>
       <c r="E24" s="15">
-        <v>2.1618972210068419</v>
+        <v>1.9589270665820184</v>
       </c>
       <c r="F24" s="15">
-        <v>2.1619186555679573</v>
+        <v>1.9589485011431338</v>
       </c>
       <c r="G24" s="15">
-        <v>2.1618967592061811</v>
+        <v>1.9589266047813576</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2735213458055386</v>
+        <v>2.0705511913807149</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1361753585250036</v>
+        <v>1.9332052041001802</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0362433314048283</v>
+        <v>1.8332731769800048</v>
       </c>
       <c r="L24" s="27">
-        <v>1.9206142648483318</v>
+        <v>1.7176441104235083</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8746475125038311</v>
+        <v>1.6716773580790076</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8222742429849814</v>
+        <v>1.619304088560158</v>
       </c>
       <c r="O24" s="12"/>
       <c r="Q24" s="24"/>
@@ -18671,22 +18681,22 @@
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
       <c r="O28" s="12"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
@@ -19571,40 +19581,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.2935780200223368</v>
+        <v>2.0906078655975131</v>
       </c>
       <c r="C48" s="15">
-        <v>2.2935781106265067</v>
+        <v>2.0906079562016835</v>
       </c>
       <c r="D48" s="15">
-        <v>2.2935781106889417</v>
+        <v>2.090607956264118</v>
       </c>
       <c r="E48" s="15">
-        <v>2.2935153584728227</v>
+        <v>2.0905452040479995</v>
       </c>
       <c r="F48" s="15">
-        <v>2.2935781107040358</v>
+        <v>2.0906079562792126</v>
       </c>
       <c r="G48" s="15">
-        <v>2.2935781107004884</v>
+        <v>2.0906079562756652</v>
       </c>
       <c r="I48" s="27">
-        <v>2.2935781081460154</v>
+        <v>2.0906079537211921</v>
       </c>
       <c r="J48" s="27">
-        <v>2.1767640241950699</v>
+        <v>1.9737938697702464</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1077866279398716</v>
+        <v>1.9048164735150481</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0360232157481168</v>
+        <v>1.8330530613232934</v>
       </c>
       <c r="M48" s="27">
-        <v>1.9713718047335693</v>
+        <v>1.7684016503087459</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9211172040494982</v>
+        <v>1.7181470496246747</v>
       </c>
       <c r="O48" s="12"/>
     </row>
@@ -19683,6 +19693,36 @@
       <c r="M51" s="12"/>
       <c r="N51" s="12"/>
       <c r="O51" s="12"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+      <c r="I52" s="12"/>
+      <c r="J52" s="12"/>
+      <c r="K52" s="12"/>
+      <c r="L52" s="12"/>
+      <c r="M52" s="12"/>
+      <c r="N52" s="12"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
+      <c r="I53" s="12"/>
+      <c r="J53" s="12"/>
+      <c r="K53" s="12"/>
+      <c r="L53" s="12"/>
+      <c r="M53" s="12"/>
+      <c r="N53" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -19704,7 +19744,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="30.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -19732,22 +19772,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
       <c r="O4" s="12"/>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.2">
@@ -20688,40 +20728,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.1619203257699602</v>
+        <v>1.9589501713451367</v>
       </c>
       <c r="C24" s="15">
-        <v>2.1618639465083289</v>
+        <v>1.9588937920835054</v>
       </c>
       <c r="D24" s="15">
-        <v>2.1618701885910707</v>
+        <v>1.9589000341662473</v>
       </c>
       <c r="E24" s="15">
-        <v>2.1618972210068419</v>
+        <v>1.9589270665820184</v>
       </c>
       <c r="F24" s="15">
-        <v>2.1619186555679573</v>
+        <v>1.9589485011431338</v>
       </c>
       <c r="G24" s="15">
-        <v>2.1618967592061811</v>
+        <v>1.9589266047813576</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2735213458055386</v>
+        <v>2.0705511913807149</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1361753585250036</v>
+        <v>1.9332052041001802</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0362433314048283</v>
+        <v>1.8332731769800048</v>
       </c>
       <c r="L24" s="27">
-        <v>1.9206142648483318</v>
+        <v>1.7176441104235083</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8746475125038311</v>
+        <v>1.6716773580790076</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8222742429849814</v>
+        <v>1.619304088560158</v>
       </c>
       <c r="O24" s="12"/>
       <c r="Q24" s="24"/>
@@ -20782,22 +20822,22 @@
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
       <c r="O28" s="12"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
@@ -21682,40 +21722,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.2935780200223368</v>
+        <v>2.0906078655975131</v>
       </c>
       <c r="C48" s="15">
-        <v>2.2935781106265067</v>
+        <v>2.0906079562016835</v>
       </c>
       <c r="D48" s="15">
-        <v>2.2935781106889417</v>
+        <v>2.090607956264118</v>
       </c>
       <c r="E48" s="15">
-        <v>2.2935153584728227</v>
+        <v>2.0905452040479995</v>
       </c>
       <c r="F48" s="15">
-        <v>2.2935781107040358</v>
+        <v>2.0906079562792126</v>
       </c>
       <c r="G48" s="15">
-        <v>2.2935781107004884</v>
+        <v>2.0906079562756652</v>
       </c>
       <c r="I48" s="27">
-        <v>2.2935781081460154</v>
+        <v>2.0906079537211921</v>
       </c>
       <c r="J48" s="27">
-        <v>2.1767640241950699</v>
+        <v>1.9737938697702464</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1077866279398716</v>
+        <v>1.9048164735150481</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0360232157481168</v>
+        <v>1.8330530613232934</v>
       </c>
       <c r="M48" s="27">
-        <v>1.9713718047335693</v>
+        <v>1.7684016503087459</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9211172040494982</v>
+        <v>1.7181470496246747</v>
       </c>
       <c r="O48" s="12"/>
     </row>
@@ -21760,6 +21800,66 @@
         <v>98.000000252691251</v>
       </c>
       <c r="O49" s="12"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="8"/>
+      <c r="N54" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -21821,22 +21921,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
@@ -22757,40 +22857,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.208918035493463</v>
+        <v>2.0059478810686393</v>
       </c>
       <c r="C24" s="15">
-        <v>2.2089180443743959</v>
+        <v>2.0059478899495726</v>
       </c>
       <c r="D24" s="15">
-        <v>2.2089180085476507</v>
+        <v>2.0059478541228275</v>
       </c>
       <c r="E24" s="15">
-        <v>2.2089180171439557</v>
+        <v>2.0059478627191325</v>
       </c>
       <c r="F24" s="15">
-        <v>2.2089180274562565</v>
+        <v>2.0059478730314328</v>
       </c>
       <c r="G24" s="15">
-        <v>2.2089180286230832</v>
+        <v>2.0059478741982595</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2718885266136519</v>
+        <v>2.0689183721888282</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1440460770614469</v>
+        <v>1.9410759226366234</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0826875216639755</v>
+        <v>1.8797173672391521</v>
       </c>
       <c r="L24" s="27">
-        <v>2.0023953751351882</v>
+        <v>1.7994252207103647</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8797001402794935</v>
+        <v>1.67672998585467</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8144825697117761</v>
+        <v>1.6115124152869527</v>
       </c>
       <c r="Q24" s="24"/>
       <c r="R24" s="19"/>
@@ -22844,22 +22944,22 @@
     <row r="27" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="28" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -23734,40 +23834,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.3472323491829101</v>
+        <v>2.1442621947580864</v>
       </c>
       <c r="C48" s="15">
-        <v>2.3472323490799218</v>
+        <v>2.1442621946550986</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3472323488495976</v>
+        <v>2.1442621944247744</v>
       </c>
       <c r="E48" s="15">
-        <v>2.3472323491831664</v>
+        <v>2.1442621947583431</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3472323491344831</v>
+        <v>2.1442621947096594</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3472323491832445</v>
+        <v>2.1442621947584213</v>
       </c>
       <c r="I48" s="27">
-        <v>2.3472323492958109</v>
+        <v>2.1442621948709872</v>
       </c>
       <c r="J48" s="27">
-        <v>2.2180673646194169</v>
+        <v>2.0150972101945932</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1458463528413265</v>
+        <v>1.9428761984165031</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0691968976365613</v>
+        <v>1.8662267432117379</v>
       </c>
       <c r="M48" s="27">
-        <v>1.9917833968801764</v>
+        <v>1.7888132424553529</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9248691808624778</v>
+        <v>1.7218990264376544</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -24533,22 +24633,22 @@
     </row>
     <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -25478,40 +25578,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.208918035493463</v>
+        <v>2.0059478810686393</v>
       </c>
       <c r="C24" s="15">
-        <v>2.2089180443743959</v>
+        <v>2.0059478899495726</v>
       </c>
       <c r="D24" s="15">
-        <v>2.2089180085476507</v>
+        <v>2.0059478541228275</v>
       </c>
       <c r="E24" s="15">
-        <v>2.2089180171439557</v>
+        <v>2.0059478627191325</v>
       </c>
       <c r="F24" s="15">
-        <v>2.2089180274562565</v>
+        <v>2.0059478730314328</v>
       </c>
       <c r="G24" s="15">
-        <v>2.2089180286230832</v>
+        <v>2.0059478741982595</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2718885266136519</v>
+        <v>2.0689183721888282</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1440460770614469</v>
+        <v>1.9410759226366234</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0826875216639755</v>
+        <v>1.8797173672391521</v>
       </c>
       <c r="L24" s="27">
-        <v>2.0023953751351882</v>
+        <v>1.7994252207103647</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8797001402794935</v>
+        <v>1.67672998585467</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8144825697117761</v>
+        <v>1.6115124152869527</v>
       </c>
       <c r="P24" s="30"/>
       <c r="Q24" s="28"/>
@@ -25573,22 +25673,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -26463,40 +26563,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.3472323491829101</v>
+        <v>2.1442621947580864</v>
       </c>
       <c r="C48" s="15">
-        <v>2.3472323490799218</v>
+        <v>2.1442621946550986</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3472323488495976</v>
+        <v>2.1442621944247744</v>
       </c>
       <c r="E48" s="15">
-        <v>2.3472323491831664</v>
+        <v>2.1442621947583431</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3472323491344831</v>
+        <v>2.1442621947096594</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3472323491832445</v>
+        <v>2.1442621947584213</v>
       </c>
       <c r="I48" s="27">
-        <v>2.3472323492958109</v>
+        <v>2.1442621948709872</v>
       </c>
       <c r="J48" s="27">
-        <v>2.2180673646194169</v>
+        <v>2.0150972101945932</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1458463528413265</v>
+        <v>1.9428761984165031</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0691968976365613</v>
+        <v>1.8662267432117379</v>
       </c>
       <c r="M48" s="27">
-        <v>1.9917833968801764</v>
+        <v>1.7888132424553529</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9248691808624778</v>
+        <v>1.7218990264376544</v>
       </c>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.15">
@@ -27680,22 +27780,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
@@ -28616,40 +28716,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.1768592907937854</v>
+        <v>1.9738891363689619</v>
       </c>
       <c r="C24" s="15">
-        <v>2.1768593164086258</v>
+        <v>1.9738891619838024</v>
       </c>
       <c r="D24" s="15">
-        <v>2.1768593161513157</v>
+        <v>1.9738891617264922</v>
       </c>
       <c r="E24" s="15">
-        <v>2.1768593212240575</v>
+        <v>1.973889166799234</v>
       </c>
       <c r="F24" s="15">
-        <v>2.1768593146978259</v>
+        <v>1.9738891602730024</v>
       </c>
       <c r="G24" s="15">
-        <v>2.1768593173456106</v>
+        <v>1.9738891629207871</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2576200331476071</v>
+        <v>2.0546498787227838</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1454682198500095</v>
+        <v>1.942498065425186</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0624410488075671</v>
+        <v>1.8594708943827436</v>
       </c>
       <c r="L24" s="27">
-        <v>1.9861009541056691</v>
+        <v>1.7831307996808456</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8907122686344418</v>
+        <v>1.6877421142096183</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8174047467626357</v>
+        <v>1.6144345923378123</v>
       </c>
       <c r="Q24" s="24"/>
       <c r="R24" s="19"/>
@@ -28703,22 +28803,22 @@
     <row r="27" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="28" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -29593,40 +29693,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.3071184896556325</v>
+        <v>2.1041483352308088</v>
       </c>
       <c r="C48" s="15">
-        <v>2.3071184880923048</v>
+        <v>2.1041483336674816</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3071184861235312</v>
+        <v>2.104148331698708</v>
       </c>
       <c r="E48" s="15">
-        <v>2.3071184877890585</v>
+        <v>2.1041483333642352</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3071184853928841</v>
+        <v>2.1041483309680604</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3071184874711985</v>
+        <v>2.1041483330463748</v>
       </c>
       <c r="I48" s="27">
-        <v>2.3071180321695755</v>
+        <v>2.1041478777447518</v>
       </c>
       <c r="J48" s="27">
-        <v>2.1881137128570436</v>
+        <v>1.9851435584322201</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1191362516859473</v>
+        <v>1.9161660972611239</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0488512671525387</v>
+        <v>1.8458811127277153</v>
       </c>
       <c r="M48" s="27">
-        <v>1.9786635263969268</v>
+        <v>1.7756933719721033</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9259415458966467</v>
+        <v>1.7229713914718232</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -29861,22 +29961,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
@@ -30797,40 +30897,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.193060828376753</v>
+        <v>1.9900906739519295</v>
       </c>
       <c r="C24" s="15">
-        <v>2.1930608578466306</v>
+        <v>1.9900907034218072</v>
       </c>
       <c r="D24" s="15">
-        <v>2.193060815199706</v>
+        <v>1.9900906607748825</v>
       </c>
       <c r="E24" s="15">
-        <v>2.1930608686122079</v>
+        <v>1.9900907141873845</v>
       </c>
       <c r="F24" s="15">
-        <v>2.1930608568168415</v>
+        <v>1.990090702392018</v>
       </c>
       <c r="G24" s="15">
-        <v>2.1929741765269517</v>
+        <v>1.9900040221021282</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2807433714698768</v>
+        <v>2.0777732170450536</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1468581346730504</v>
+        <v>1.943887980248227</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0722612615527312</v>
+        <v>1.8692911071279077</v>
       </c>
       <c r="L24" s="27">
-        <v>1.9505059971755432</v>
+        <v>1.7475358427507197</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8747312877997131</v>
+        <v>1.6717611333748896</v>
       </c>
       <c r="N24" s="27">
-        <v>1.7802219647848936</v>
+        <v>1.5772518103600701</v>
       </c>
       <c r="Q24" s="24"/>
       <c r="R24" s="19"/>
@@ -30884,22 +30984,22 @@
     <row r="27" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="28" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -31774,40 +31874,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.3291994818950443</v>
+        <v>2.1262293274702211</v>
       </c>
       <c r="C48" s="15">
-        <v>2.3291994930958064</v>
+        <v>2.1262293386709832</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3291994898564901</v>
+        <v>2.1262293354316668</v>
       </c>
       <c r="E48" s="15">
-        <v>2.3291994604252184</v>
+        <v>2.1262293060003952</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3291994961538234</v>
+        <v>2.1262293417290001</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3291994438989674</v>
+        <v>2.1262292894741437</v>
       </c>
       <c r="I48" s="27">
-        <v>2.4087414751307223</v>
+        <v>2.2057713207058987</v>
       </c>
       <c r="J48" s="27">
-        <v>2.2903320168507899</v>
+        <v>2.0873618624259667</v>
       </c>
       <c r="K48" s="27">
-        <v>2.2158311419654946</v>
+        <v>2.0128609875406713</v>
       </c>
       <c r="L48" s="27">
-        <v>2.1637796569779257</v>
+        <v>1.9608095025531023</v>
       </c>
       <c r="M48" s="27">
-        <v>2.0570555049759505</v>
+        <v>1.854085350551127</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9939166752232211</v>
+        <v>1.7909465207983977</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -31869,19 +31969,6 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A51" s="12"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12"/>
-      <c r="K51" s="12"/>
-      <c r="L51" s="12"/>
-      <c r="M51" s="12"/>
-      <c r="N51" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -31931,22 +32018,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
       <c r="O4" s="12"/>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.2">
@@ -32887,40 +32974,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.1719203257699604</v>
+        <v>1.9689501713451369</v>
       </c>
       <c r="C24" s="15">
-        <v>2.1718639465083291</v>
+        <v>1.9688937920835057</v>
       </c>
       <c r="D24" s="15">
-        <v>2.1718701885910709</v>
+        <v>1.9689000341662475</v>
       </c>
       <c r="E24" s="15">
-        <v>2.1718972210068421</v>
+        <v>1.9689270665820187</v>
       </c>
       <c r="F24" s="15">
-        <v>2.1719186555679575</v>
+        <v>1.968948501143134</v>
       </c>
       <c r="G24" s="15">
-        <v>2.1718967592061813</v>
+        <v>1.9689266047813578</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2835213458055388</v>
+        <v>2.0805511913807155</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1461753585250039</v>
+        <v>1.9432052041001804</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0462433314048285</v>
+        <v>1.843273176980005</v>
       </c>
       <c r="L24" s="27">
-        <v>1.9306142648483318</v>
+        <v>1.7276441104235083</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8846475125038311</v>
+        <v>1.6816773580790076</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8322742429849814</v>
+        <v>1.629304088560158</v>
       </c>
       <c r="O24" s="12"/>
       <c r="Q24" s="24"/>
@@ -32981,22 +33068,22 @@
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
       <c r="O28" s="12"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
@@ -33881,40 +33968,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.303578020022337</v>
+        <v>2.1006078655975138</v>
       </c>
       <c r="C48" s="15">
-        <v>2.303578110626507</v>
+        <v>2.1006079562016833</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3035781106889419</v>
+        <v>2.1006079562641187</v>
       </c>
       <c r="E48" s="15">
-        <v>2.303515358472823</v>
+        <v>2.1005452040479993</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3035781107040361</v>
+        <v>2.1006079562792124</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3035781107004887</v>
+        <v>2.100607956275665</v>
       </c>
       <c r="I48" s="27">
-        <v>2.3035781081460156</v>
+        <v>2.1006079537211919</v>
       </c>
       <c r="J48" s="27">
-        <v>2.1867640241950701</v>
+        <v>1.9837938697702466</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1177866279398718</v>
+        <v>1.9148164735150484</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0460232157481171</v>
+        <v>1.8430530613232936</v>
       </c>
       <c r="M48" s="27">
-        <v>1.9813718047335693</v>
+        <v>1.7784016503087459</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9311172040494982</v>
+        <v>1.7281470496246747</v>
       </c>
       <c r="O48" s="12"/>
     </row>
@@ -34082,7 +34169,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W50"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="30.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -34109,22 +34196,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
@@ -35045,40 +35132,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.2222001829512301</v>
+        <v>2.0192300285264064</v>
       </c>
       <c r="C24" s="15">
-        <v>2.2222001907806077</v>
+        <v>2.0192300363557845</v>
       </c>
       <c r="D24" s="15">
-        <v>2.2222001945343668</v>
+        <v>2.0192300401095435</v>
       </c>
       <c r="E24" s="15">
-        <v>2.2222001898183192</v>
+        <v>2.0192300353934955</v>
       </c>
       <c r="F24" s="15">
-        <v>2.2222002038198432</v>
+        <v>2.0192300493950199</v>
       </c>
       <c r="G24" s="15">
-        <v>2.2222001929869513</v>
+        <v>2.019230038562128</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2897372948348313</v>
+        <v>2.0867671404100081</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1778207944960633</v>
+        <v>1.9748506400712398</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0984811289617236</v>
+        <v>1.8955109745369001</v>
       </c>
       <c r="L24" s="27">
-        <v>2.0084968502169325</v>
+        <v>1.805526695792109</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8926644212541344</v>
+        <v>1.6896942668293109</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8299041897505712</v>
+        <v>1.6269340353257478</v>
       </c>
       <c r="Q24" s="24"/>
       <c r="R24" s="19"/>
@@ -35132,22 +35219,22 @@
     <row r="27" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="28" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -36022,40 +36109,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.3588621610897929</v>
+        <v>2.1558920066649696</v>
       </c>
       <c r="C48" s="15">
-        <v>2.3588621655420887</v>
+        <v>2.155892011117265</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3588621586552292</v>
+        <v>2.1558920042304059</v>
       </c>
       <c r="E48" s="15">
-        <v>2.3588621645187482</v>
+        <v>2.1558920100939245</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3588621716151135</v>
+        <v>2.1558920171902898</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3588621586693432</v>
+        <v>2.15589200424452</v>
       </c>
       <c r="I48" s="27">
-        <v>2.3588621529306755</v>
+        <v>2.1558919985058518</v>
       </c>
       <c r="J48" s="27">
-        <v>2.2350865629903365</v>
+        <v>2.0321164085655132</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1659494605241751</v>
+        <v>1.9629793060993517</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0907240055171075</v>
+        <v>1.887753851092284</v>
       </c>
       <c r="M48" s="27">
-        <v>2.0129008155227881</v>
+        <v>1.8099306610979646</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9340548835698248</v>
+        <v>1.7310847291450013</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -36114,6 +36201,51 @@
       <c r="L50" s="12"/>
       <c r="M50" s="12"/>
       <c r="N50" s="12"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -36162,22 +36294,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
@@ -37098,40 +37230,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.1719203257699604</v>
+        <v>1.9689501713451369</v>
       </c>
       <c r="C24" s="15">
-        <v>2.1718639465083291</v>
+        <v>1.9688937920835057</v>
       </c>
       <c r="D24" s="15">
-        <v>2.1718701885910709</v>
+        <v>1.9689000341662475</v>
       </c>
       <c r="E24" s="15">
-        <v>2.1718972210068421</v>
+        <v>1.9689270665820187</v>
       </c>
       <c r="F24" s="15">
-        <v>2.1719186555679575</v>
+        <v>1.968948501143134</v>
       </c>
       <c r="G24" s="15">
-        <v>2.1718967592061813</v>
+        <v>1.9689266047813578</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2835213458055388</v>
+        <v>2.0805511913807155</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1461753585250039</v>
+        <v>1.9432052041001804</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0462433314048285</v>
+        <v>1.843273176980005</v>
       </c>
       <c r="L24" s="27">
-        <v>1.9306142648483318</v>
+        <v>1.7276441104235083</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8846475125038311</v>
+        <v>1.6816773580790076</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8322742429849814</v>
+        <v>1.629304088560158</v>
       </c>
       <c r="Q24" s="24"/>
       <c r="R24" s="19"/>
@@ -37185,22 +37317,22 @@
     <row r="27" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="28" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -38075,40 +38207,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.303578020022337</v>
+        <v>2.1006078655975138</v>
       </c>
       <c r="C48" s="15">
-        <v>2.303578110626507</v>
+        <v>2.1006079562016833</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3035781106889419</v>
+        <v>2.1006079562641187</v>
       </c>
       <c r="E48" s="15">
-        <v>2.303515358472823</v>
+        <v>2.1005452040479993</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3035781107040361</v>
+        <v>2.1006079562792124</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3035781107004887</v>
+        <v>2.100607956275665</v>
       </c>
       <c r="I48" s="27">
-        <v>2.3035781081460156</v>
+        <v>2.1006079537211919</v>
       </c>
       <c r="J48" s="27">
-        <v>2.1867640241950701</v>
+        <v>1.9837938697702466</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1177866279398718</v>
+        <v>1.9148164735150484</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0460232157481171</v>
+        <v>1.8430530613232936</v>
       </c>
       <c r="M48" s="27">
-        <v>1.9813718047335693</v>
+        <v>1.7784016503087459</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9311172040494982</v>
+        <v>1.7281470496246747</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -38170,51 +38302,12 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A51" s="12"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12"/>
-      <c r="K51" s="12"/>
-      <c r="L51" s="12"/>
-      <c r="M51" s="12"/>
-      <c r="N51" s="12"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A52" s="12"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
-      <c r="I52" s="12"/>
-      <c r="J52" s="12"/>
-      <c r="K52" s="12"/>
-      <c r="L52" s="12"/>
-      <c r="M52" s="12"/>
-      <c r="N52" s="12"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A53" s="12"/>
-      <c r="B53" s="12"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="12"/>
-      <c r="J53" s="12"/>
-      <c r="K53" s="12"/>
-      <c r="L53" s="12"/>
-      <c r="M53" s="12"/>
-      <c r="N53" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -38263,22 +38356,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
@@ -39199,40 +39292,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.1919203257699604</v>
+        <v>1.988950171345137</v>
       </c>
       <c r="C24" s="15">
-        <v>2.1918639465083292</v>
+        <v>1.9888937920835057</v>
       </c>
       <c r="D24" s="15">
-        <v>2.191870188591071</v>
+        <v>1.9889000341662475</v>
       </c>
       <c r="E24" s="15">
-        <v>2.1918972210068421</v>
+        <v>1.9889270665820187</v>
       </c>
       <c r="F24" s="15">
-        <v>2.1919186555679575</v>
+        <v>1.988948501143134</v>
       </c>
       <c r="G24" s="15">
-        <v>2.1918967592061813</v>
+        <v>1.9889266047813579</v>
       </c>
       <c r="I24" s="27">
-        <v>2.3035213458055388</v>
+        <v>2.1005511913807151</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1661753585250039</v>
+        <v>1.9632052041001804</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0662433314048285</v>
+        <v>1.8632731769800051</v>
       </c>
       <c r="L24" s="27">
-        <v>1.9506142648483318</v>
+        <v>1.7476441104235083</v>
       </c>
       <c r="M24" s="27">
-        <v>1.9046475125038311</v>
+        <v>1.7016773580790077</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8522742429849814</v>
+        <v>1.649304088560158</v>
       </c>
       <c r="Q24" s="24"/>
       <c r="R24" s="19"/>
@@ -39286,22 +39379,22 @@
     <row r="27" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="28" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -40176,40 +40269,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.323578020022337</v>
+        <v>2.1206078655975134</v>
       </c>
       <c r="C48" s="15">
-        <v>2.323578110626507</v>
+        <v>2.1206079562016837</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3235781106889419</v>
+        <v>2.1206079562641182</v>
       </c>
       <c r="E48" s="15">
-        <v>2.323515358472823</v>
+        <v>2.1205452040479997</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3235781107040361</v>
+        <v>2.1206079562792128</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3235781107004887</v>
+        <v>2.1206079562756655</v>
       </c>
       <c r="I48" s="27">
-        <v>2.3235781081460156</v>
+        <v>2.1206079537211924</v>
       </c>
       <c r="J48" s="27">
-        <v>2.2067640241950701</v>
+        <v>2.0037938697702469</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1377866279398718</v>
+        <v>1.9348164735150484</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0660232157481171</v>
+        <v>1.8630530613232936</v>
       </c>
       <c r="M48" s="27">
-        <v>2.0013718047335693</v>
+        <v>1.7984016503087459</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9511172040494982</v>
+        <v>1.7481470496246747</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -40273,7 +40366,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="30.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -40300,22 +40393,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
@@ -41236,40 +41329,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.228918035493463</v>
+        <v>2.0259478810686398</v>
       </c>
       <c r="C24" s="15">
-        <v>2.2289180443743959</v>
+        <v>2.0259478899495722</v>
       </c>
       <c r="D24" s="15">
-        <v>2.2289180085476508</v>
+        <v>2.0259478541228271</v>
       </c>
       <c r="E24" s="15">
-        <v>2.2289180171439558</v>
+        <v>2.0259478627191321</v>
       </c>
       <c r="F24" s="15">
-        <v>2.2289180274562566</v>
+        <v>2.0259478730314333</v>
       </c>
       <c r="G24" s="15">
-        <v>2.2289180286230832</v>
+        <v>2.0259478741982599</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2918885266136519</v>
+        <v>2.0889183721888287</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1640460770614469</v>
+        <v>1.9610759226366234</v>
       </c>
       <c r="K24" s="27">
-        <v>2.1026875216639755</v>
+        <v>1.8997173672391521</v>
       </c>
       <c r="L24" s="27">
-        <v>2.0223953751351882</v>
+        <v>1.8194252207103647</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8997001402794935</v>
+        <v>1.6967299858546701</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8344825697117761</v>
+        <v>1.6315124152869527</v>
       </c>
       <c r="Q24" s="24"/>
       <c r="R24" s="19"/>
@@ -41323,22 +41416,22 @@
     <row r="27" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="28" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -42213,43 +42306,43 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.3672323491829101</v>
+        <v>2.1642621947580869</v>
       </c>
       <c r="C48" s="15">
-        <v>2.3672323490799219</v>
+        <v>2.1642621946550982</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3672323488495977</v>
+        <v>2.164262194424774</v>
       </c>
       <c r="E48" s="15">
-        <v>2.3672323491831664</v>
+        <v>2.1642621947583427</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3672323491344831</v>
+        <v>2.1642621947096599</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3672323491832445</v>
+        <v>2.1642621947584209</v>
       </c>
       <c r="I48" s="27">
-        <v>2.3672323492958109</v>
+        <v>2.1642621948709877</v>
       </c>
       <c r="J48" s="27">
-        <v>2.2380673646194169</v>
+        <v>2.0350972101945937</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1658463528413265</v>
+        <v>1.9628761984165031</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0891968976365614</v>
+        <v>1.8862267432117379</v>
       </c>
       <c r="M48" s="27">
-        <v>2.0117833968801762</v>
+        <v>1.8088132424553527</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9448691808624778</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.15">
+        <v>1.7418990264376544</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A49" s="20" t="s">
         <v>30</v>
       </c>
@@ -42289,6 +42382,86 @@
       <c r="N49" s="26">
         <v>98.000000013210723</v>
       </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+      <c r="O51" s="8"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+      <c r="O52" s="8"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
+      <c r="O53" s="8"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="8"/>
+      <c r="N54" s="8"/>
+      <c r="O54" s="8"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="8"/>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="8"/>
+      <c r="M55" s="8"/>
+      <c r="N55" s="8"/>
+      <c r="O55" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -42337,22 +42510,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
@@ -43273,40 +43446,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.2122001829512299</v>
+        <v>2.0092300285264066</v>
       </c>
       <c r="C24" s="15">
-        <v>2.2122001907806075</v>
+        <v>2.0092300363557838</v>
       </c>
       <c r="D24" s="15">
-        <v>2.2122001945343666</v>
+        <v>2.0092300401095429</v>
       </c>
       <c r="E24" s="15">
-        <v>2.212200189818319</v>
+        <v>2.0092300353934958</v>
       </c>
       <c r="F24" s="15">
-        <v>2.2122002038198429</v>
+        <v>2.0092300493950193</v>
       </c>
       <c r="G24" s="15">
-        <v>2.212200192986951</v>
+        <v>2.0092300385621273</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2797372948348311</v>
+        <v>2.0767671404100074</v>
       </c>
       <c r="J24" s="27">
-        <v>2.167820794496063</v>
+        <v>1.9648506400712396</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0884811289617233</v>
+        <v>1.8855109745368999</v>
       </c>
       <c r="L24" s="27">
-        <v>1.9984968502169325</v>
+        <v>1.795526695792109</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8826644212541344</v>
+        <v>1.6796942668293109</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8199041897505712</v>
+        <v>1.6169340353257478</v>
       </c>
       <c r="Q24" s="24"/>
       <c r="R24" s="19"/>
@@ -43360,22 +43533,22 @@
     <row r="27" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="28" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -44250,40 +44423,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.3488621610897926</v>
+        <v>2.1458920066649689</v>
       </c>
       <c r="C48" s="15">
-        <v>2.3488621655420885</v>
+        <v>2.1458920111172652</v>
       </c>
       <c r="D48" s="15">
-        <v>2.348862158655229</v>
+        <v>2.1458920042304053</v>
       </c>
       <c r="E48" s="15">
-        <v>2.348862164518748</v>
+        <v>2.1458920100939247</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3488621716151132</v>
+        <v>2.14589201719029</v>
       </c>
       <c r="G48" s="15">
-        <v>2.348862158669343</v>
+        <v>2.1458920042445193</v>
       </c>
       <c r="I48" s="27">
-        <v>2.3488621529306752</v>
+        <v>2.145891998505852</v>
       </c>
       <c r="J48" s="27">
-        <v>2.2250865629903362</v>
+        <v>2.0221164085655126</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1559494605241749</v>
+        <v>1.9529793060993514</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0807240055171072</v>
+        <v>1.8777538510922838</v>
       </c>
       <c r="M48" s="27">
-        <v>2.0029008155227879</v>
+        <v>1.7999306610979644</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9240548835698248</v>
+        <v>1.7210847291450013</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -44345,19 +44518,6 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A51" s="12"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12"/>
-      <c r="K51" s="12"/>
-      <c r="L51" s="12"/>
-      <c r="M51" s="12"/>
-      <c r="N51" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -44406,22 +44566,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
@@ -45342,40 +45502,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.248918035493463</v>
+        <v>2.0459478810686393</v>
       </c>
       <c r="C24" s="15">
-        <v>2.2489180443743959</v>
+        <v>2.0459478899495727</v>
       </c>
       <c r="D24" s="15">
-        <v>2.2489180085476508</v>
+        <v>2.0459478541228275</v>
       </c>
       <c r="E24" s="15">
-        <v>2.2489180171439558</v>
+        <v>2.0459478627191325</v>
       </c>
       <c r="F24" s="15">
-        <v>2.2489180274562566</v>
+        <v>2.0459478730314329</v>
       </c>
       <c r="G24" s="15">
-        <v>2.2489180286230832</v>
+        <v>2.0459478741982595</v>
       </c>
       <c r="I24" s="27">
-        <v>2.311888526613652</v>
+        <v>2.1089183721888283</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1840460770614469</v>
+        <v>1.9810759226366235</v>
       </c>
       <c r="K24" s="27">
-        <v>2.1226875216639756</v>
+        <v>1.9197173672391521</v>
       </c>
       <c r="L24" s="27">
-        <v>2.0423953751351882</v>
+        <v>1.8394252207103647</v>
       </c>
       <c r="M24" s="27">
-        <v>1.9197001402794935</v>
+        <v>1.7167299858546701</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8544825697117762</v>
+        <v>1.6515124152869527</v>
       </c>
       <c r="Q24" s="24"/>
       <c r="R24" s="19"/>
@@ -45429,22 +45589,22 @@
     <row r="27" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="28" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -46319,40 +46479,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.3872323491829102</v>
+        <v>2.1842621947580865</v>
       </c>
       <c r="C48" s="15">
-        <v>2.3872323490799219</v>
+        <v>2.1842621946550986</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3872323488495977</v>
+        <v>2.1842621944247744</v>
       </c>
       <c r="E48" s="15">
-        <v>2.3872323491831664</v>
+        <v>2.1842621947583432</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3872323491344831</v>
+        <v>2.1842621947096594</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3872323491832446</v>
+        <v>2.1842621947584213</v>
       </c>
       <c r="I48" s="27">
-        <v>2.387232349295811</v>
+        <v>2.1842621948709873</v>
       </c>
       <c r="J48" s="27">
-        <v>2.2580673646194169</v>
+        <v>2.0550972101945932</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1858463528413266</v>
+        <v>1.9828761984165031</v>
       </c>
       <c r="L48" s="27">
-        <v>2.1091968976365614</v>
+        <v>1.9062267432117379</v>
       </c>
       <c r="M48" s="27">
-        <v>2.0317833968801762</v>
+        <v>1.8288132424553527</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9648691808624779</v>
+        <v>1.7618990264376544</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -46416,7 +46576,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W50"/>
+  <dimension ref="A1:W58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="30.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -46444,22 +46604,22 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
       <c r="O4" s="12"/>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.2">
@@ -47400,40 +47560,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.3012696138746342</v>
+        <v>2.0982994594498106</v>
       </c>
       <c r="C24" s="15">
-        <v>2.3012696138746316</v>
+        <v>2.0982994594498079</v>
       </c>
       <c r="D24" s="15">
-        <v>2.3012696138746391</v>
+        <v>2.0982994594498159</v>
       </c>
       <c r="E24" s="15">
-        <v>2.3012696138746187</v>
+        <v>2.0982994594497955</v>
       </c>
       <c r="F24" s="15">
-        <v>2.3012696138746565</v>
+        <v>2.0982994594498328</v>
       </c>
       <c r="G24" s="15">
-        <v>2.3012696138747009</v>
+        <v>2.0982994594498772</v>
       </c>
       <c r="I24" s="27">
-        <v>2.3166256076660452</v>
+        <v>2.1136554532412219</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1871391231293615</v>
+        <v>1.9841689687045381</v>
       </c>
       <c r="K24" s="27">
-        <v>2.1049583993618635</v>
+        <v>1.90198824493704</v>
       </c>
       <c r="L24" s="27">
-        <v>1.9955214359084816</v>
+        <v>1.7925512814836582</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8860101684385233</v>
+        <v>1.6830400140136998</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8207968279973312</v>
+        <v>1.6178266735725078</v>
       </c>
       <c r="O24" s="12"/>
       <c r="Q24" s="24"/>
@@ -47494,22 +47654,22 @@
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
       <c r="O28" s="12"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
@@ -48394,40 +48554,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.4250613440527409</v>
+        <v>2.2220911896279176</v>
       </c>
       <c r="C48" s="15">
-        <v>2.4250638784350689</v>
+        <v>2.2220937240102456</v>
       </c>
       <c r="D48" s="15">
-        <v>2.4250618159354027</v>
+        <v>2.2220916615105795</v>
       </c>
       <c r="E48" s="15">
-        <v>2.4250634042193076</v>
+        <v>2.2220932497944839</v>
       </c>
       <c r="F48" s="15">
-        <v>2.4250613438419126</v>
+        <v>2.2220911894170889</v>
       </c>
       <c r="G48" s="15">
-        <v>2.4250622985764885</v>
+        <v>2.2220921441516648</v>
       </c>
       <c r="I48" s="27">
-        <v>2.4395170472119352</v>
+        <v>2.2365468927871115</v>
       </c>
       <c r="J48" s="27">
-        <v>2.3166996248095315</v>
+        <v>2.1137294703847083</v>
       </c>
       <c r="K48" s="27">
-        <v>2.2397857028474437</v>
+        <v>2.03681554842262</v>
       </c>
       <c r="L48" s="27">
-        <v>2.1571036682962683</v>
+        <v>1.9541335138714448</v>
       </c>
       <c r="M48" s="27">
-        <v>2.0617341526156601</v>
+        <v>1.8587639981908366</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9666221559777921</v>
+        <v>1.7636520015529686</v>
       </c>
       <c r="O48" s="12"/>
     </row>
@@ -48489,6 +48649,126 @@
       <c r="M50" s="12"/>
       <c r="N50" s="12"/>
       <c r="O50" s="12"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="8"/>
+      <c r="N54" s="8"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="8"/>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="8"/>
+      <c r="M55" s="8"/>
+      <c r="N55" s="8"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="8"/>
+      <c r="I56" s="8"/>
+      <c r="J56" s="8"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="8"/>
+      <c r="M56" s="8"/>
+      <c r="N56" s="8"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="B57" s="8"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="8"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="8"/>
+      <c r="I57" s="8"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="8"/>
+      <c r="M57" s="8"/>
+      <c r="N57" s="8"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8"/>
+      <c r="I58" s="8"/>
+      <c r="J58" s="8"/>
+      <c r="K58" s="8"/>
+      <c r="L58" s="8"/>
+      <c r="M58" s="8"/>
+      <c r="N58" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -48510,7 +48790,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W52"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.33203125" style="8" customWidth="1"/>
@@ -48537,22 +48817,22 @@
     </row>
     <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -49464,40 +49744,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.193060828376753</v>
+        <v>1.9900906739519295</v>
       </c>
       <c r="C24" s="15">
-        <v>2.1930608578466306</v>
+        <v>1.9900907034218072</v>
       </c>
       <c r="D24" s="15">
-        <v>2.193060815199706</v>
+        <v>1.9900906607748825</v>
       </c>
       <c r="E24" s="15">
-        <v>2.1930608686122079</v>
+        <v>1.9900907141873845</v>
       </c>
       <c r="F24" s="15">
-        <v>2.1930608568168415</v>
+        <v>1.990090702392018</v>
       </c>
       <c r="G24" s="15">
-        <v>2.1929741765269517</v>
+        <v>1.9900040221021282</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2807433714698768</v>
+        <v>2.0777732170450536</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1468581346730504</v>
+        <v>1.943887980248227</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0722612615527312</v>
+        <v>1.8692911071279077</v>
       </c>
       <c r="L24" s="27">
-        <v>1.9505059971755432</v>
+        <v>1.7475358427507197</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8747312877997131</v>
+        <v>1.6717611333748896</v>
       </c>
       <c r="N24" s="27">
-        <v>1.7802219647848936</v>
+        <v>1.5772518103600701</v>
       </c>
       <c r="Q24" s="28"/>
       <c r="R24" s="18"/>
@@ -49557,22 +49837,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -50447,40 +50727,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.3291994818950443</v>
+        <v>2.1262293274702211</v>
       </c>
       <c r="C48" s="15">
-        <v>2.3291994930958064</v>
+        <v>2.1262293386709832</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3291994898564901</v>
+        <v>2.1262293354316668</v>
       </c>
       <c r="E48" s="15">
-        <v>2.3291994604252184</v>
+        <v>2.1262293060003952</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3291994961538234</v>
+        <v>2.1262293417290001</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3291994438989674</v>
+        <v>2.1262292894741437</v>
       </c>
       <c r="I48" s="27">
-        <v>2.4087414751307223</v>
+        <v>2.2057713207058987</v>
       </c>
       <c r="J48" s="27">
-        <v>2.2903320168507899</v>
+        <v>2.0873618624259667</v>
       </c>
       <c r="K48" s="27">
-        <v>2.2158311419654946</v>
+        <v>2.0128609875406713</v>
       </c>
       <c r="L48" s="27">
-        <v>2.1637796569779257</v>
+        <v>1.9608095025531023</v>
       </c>
       <c r="M48" s="27">
-        <v>2.0570555049759505</v>
+        <v>1.854085350551127</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9939166752232211</v>
+        <v>1.7909465207983977</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -50571,6 +50851,21 @@
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -50622,22 +50917,22 @@
     </row>
     <row r="4" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
       <c r="O4" s="12"/>
     </row>
     <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.15">
@@ -51453,40 +51748,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.1819203257699602</v>
+        <v>1.9789501713451367</v>
       </c>
       <c r="C24" s="15">
-        <v>2.1818639465083289</v>
+        <v>1.9788937920835055</v>
       </c>
       <c r="D24" s="15">
-        <v>2.1818701885910707</v>
+        <v>1.9789000341662473</v>
       </c>
       <c r="E24" s="15">
-        <v>2.1818972210068419</v>
+        <v>1.9789270665820184</v>
       </c>
       <c r="F24" s="15">
-        <v>2.1819186555679573</v>
+        <v>1.9789485011431338</v>
       </c>
       <c r="G24" s="15">
-        <v>2.1818967592061811</v>
+        <v>1.9789266047813576</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2935213458055386</v>
+        <v>2.0905511913807153</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1561753585250036</v>
+        <v>1.9532052041001802</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0562433314048283</v>
+        <v>1.8532731769800048</v>
       </c>
       <c r="L24" s="27">
-        <v>1.9406142648483318</v>
+        <v>1.7376441104235083</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8946475125038311</v>
+        <v>1.6916773580790077</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8422742429849814</v>
+        <v>1.639304088560158</v>
       </c>
       <c r="O24" s="12"/>
     </row>
@@ -51540,22 +51835,22 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
       <c r="O28" s="12"/>
     </row>
     <row r="29" spans="1:15" ht="30" x14ac:dyDescent="0.15">
@@ -52361,40 +52656,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.3135780200223368</v>
+        <v>2.1106078655975136</v>
       </c>
       <c r="C48" s="15">
-        <v>2.3135781106265068</v>
+        <v>2.1106079562016831</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3135781106889417</v>
+        <v>2.1106079562641185</v>
       </c>
       <c r="E48" s="15">
-        <v>2.3135153584728227</v>
+        <v>2.1105452040479991</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3135781107040359</v>
+        <v>2.1106079562792122</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3135781107004885</v>
+        <v>2.1106079562756648</v>
       </c>
       <c r="I48" s="27">
-        <v>2.3135781081460154</v>
+        <v>2.1106079537211917</v>
       </c>
       <c r="J48" s="27">
-        <v>2.1967640241950699</v>
+        <v>1.9937938697702464</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1277866279398716</v>
+        <v>1.9248164735150481</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0560232157481169</v>
+        <v>1.8530530613232934</v>
       </c>
       <c r="M48" s="27">
-        <v>1.9913718047335693</v>
+        <v>1.7884016503087459</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9411172040494982</v>
+        <v>1.7381470496246747</v>
       </c>
       <c r="O48" s="12"/>
     </row>
@@ -53302,22 +53597,22 @@
     </row>
     <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -54229,40 +54524,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.1768592907937854</v>
+        <v>1.9738891363689619</v>
       </c>
       <c r="C24" s="15">
-        <v>2.1768593164086258</v>
+        <v>1.9738891619838024</v>
       </c>
       <c r="D24" s="15">
-        <v>2.1768593161513157</v>
+        <v>1.9738891617264922</v>
       </c>
       <c r="E24" s="15">
-        <v>2.1768593212240575</v>
+        <v>1.973889166799234</v>
       </c>
       <c r="F24" s="15">
-        <v>2.1768593146978259</v>
+        <v>1.9738891602730024</v>
       </c>
       <c r="G24" s="15">
-        <v>2.1768593173456106</v>
+        <v>1.9738891629207871</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2576200331476071</v>
+        <v>2.0546498787227838</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1454682198500095</v>
+        <v>1.942498065425186</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0624410488075671</v>
+        <v>1.8594708943827436</v>
       </c>
       <c r="L24" s="27">
-        <v>1.9861009541056691</v>
+        <v>1.7831307996808456</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8907122686344418</v>
+        <v>1.6877421142096183</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8174047467626357</v>
+        <v>1.6144345923378123</v>
       </c>
       <c r="Q24" s="28"/>
       <c r="R24" s="18"/>
@@ -54322,22 +54617,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -55212,40 +55507,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.3071184896556325</v>
+        <v>2.1041483352308088</v>
       </c>
       <c r="C48" s="15">
-        <v>2.3071184880923048</v>
+        <v>2.1041483336674816</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3071184861235312</v>
+        <v>2.104148331698708</v>
       </c>
       <c r="E48" s="15">
-        <v>2.3071184877890585</v>
+        <v>2.1041483333642352</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3071184853928841</v>
+        <v>2.1041483309680604</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3071184874711985</v>
+        <v>2.1041483330463748</v>
       </c>
       <c r="I48" s="27">
-        <v>2.3071180321695755</v>
+        <v>2.1041478777447518</v>
       </c>
       <c r="J48" s="27">
-        <v>2.1881137128570436</v>
+        <v>1.9851435584322201</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1191362516859473</v>
+        <v>1.9161660972611239</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0488512671525387</v>
+        <v>1.8458811127277153</v>
       </c>
       <c r="M48" s="27">
-        <v>1.9786635263969268</v>
+        <v>1.7756933719721033</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9259415458966467</v>
+        <v>1.7229713914718232</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -55388,7 +55683,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="27" style="8" bestFit="1" customWidth="1"/>
@@ -55415,22 +55710,22 @@
     </row>
     <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -56342,40 +56637,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.1955181897931744</v>
+        <v>1.9925480353683509</v>
       </c>
       <c r="C24" s="15">
-        <v>2.1955181797783432</v>
+        <v>1.9925480253535197</v>
       </c>
       <c r="D24" s="15">
-        <v>2.195518183346528</v>
+        <v>1.9925480289217046</v>
       </c>
       <c r="E24" s="15">
-        <v>2.1955181804724662</v>
+        <v>1.9925480260476427</v>
       </c>
       <c r="F24" s="15">
-        <v>2.1955181705503612</v>
+        <v>1.9925480161255378</v>
       </c>
       <c r="G24" s="15">
-        <v>2.1955181678043809</v>
+        <v>1.9925480133795574</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2581548789250272</v>
+        <v>2.0551847245002035</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1350196881211354</v>
+        <v>1.9320495336963119</v>
       </c>
       <c r="K24" s="27">
-        <v>2.068864015536386</v>
+        <v>1.8658938611115625</v>
       </c>
       <c r="L24" s="27">
-        <v>2.0020712088749115</v>
+        <v>1.7991010544500881</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8810028706547974</v>
+        <v>1.678032716229974</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8449689707113528</v>
+        <v>1.6419988162865293</v>
       </c>
       <c r="Q24" s="28"/>
       <c r="R24" s="18"/>
@@ -56435,22 +56730,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -57325,40 +57620,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.3299823297159019</v>
+        <v>2.1270121752910782</v>
       </c>
       <c r="C48" s="15">
-        <v>2.3299823287878332</v>
+        <v>2.1270121743630099</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3299823285464094</v>
+        <v>2.1270121741215862</v>
       </c>
       <c r="E48" s="15">
-        <v>2.3299823295618283</v>
+        <v>2.127012175137005</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3299823285862202</v>
+        <v>2.127012174161397</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3299823292202411</v>
+        <v>2.1270121747954178</v>
       </c>
       <c r="I48" s="27">
-        <v>2.3299823296196092</v>
+        <v>2.1270121751947855</v>
       </c>
       <c r="J48" s="27">
-        <v>2.2037861655744773</v>
+        <v>2.000816011149654</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1317786520893143</v>
+        <v>1.9288084976644908</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0570225631223087</v>
+        <v>1.8540524086974852</v>
       </c>
       <c r="M48" s="27">
-        <v>1.9799214983492786</v>
+        <v>1.7769513439244551</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9239136151291363</v>
+        <v>1.7209434607043128</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -57401,6 +57696,51 @@
       <c r="N49" s="26">
         <v>98.000000160971382</v>
       </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -57421,7 +57761,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W50"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="26" style="8" bestFit="1" customWidth="1"/>
@@ -57448,22 +57788,22 @@
     </row>
     <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -58375,40 +58715,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.2019203257699602</v>
+        <v>1.9989501713451368</v>
       </c>
       <c r="C24" s="15">
-        <v>2.201863946508329</v>
+        <v>1.9988937920835055</v>
       </c>
       <c r="D24" s="15">
-        <v>2.2018701885910708</v>
+        <v>1.9989000341662473</v>
       </c>
       <c r="E24" s="15">
-        <v>2.2018972210068419</v>
+        <v>1.9989270665820185</v>
       </c>
       <c r="F24" s="15">
-        <v>2.2019186555679573</v>
+        <v>1.9989485011431338</v>
       </c>
       <c r="G24" s="15">
-        <v>2.2018967592061811</v>
+        <v>1.9989266047813576</v>
       </c>
       <c r="I24" s="27">
-        <v>2.3135213458055386</v>
+        <v>2.1105511913807149</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1761753585250037</v>
+        <v>1.9732052041001802</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0762433314048283</v>
+        <v>1.8732731769800048</v>
       </c>
       <c r="L24" s="27">
-        <v>1.9606142648483318</v>
+        <v>1.7576441104235083</v>
       </c>
       <c r="M24" s="27">
-        <v>1.9146475125038311</v>
+        <v>1.7116773580790077</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8622742429849815</v>
+        <v>1.659304088560158</v>
       </c>
       <c r="Q24" s="28"/>
       <c r="R24" s="18"/>
@@ -58468,22 +58808,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -59358,40 +59698,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.3335780200223368</v>
+        <v>2.1306078655975131</v>
       </c>
       <c r="C48" s="15">
-        <v>2.3335781106265068</v>
+        <v>2.1306079562016835</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3335781106889417</v>
+        <v>2.130607956264118</v>
       </c>
       <c r="E48" s="15">
-        <v>2.3335153584728228</v>
+        <v>2.1305452040479995</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3335781107040359</v>
+        <v>2.1306079562792126</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3335781107004885</v>
+        <v>2.1306079562756652</v>
       </c>
       <c r="I48" s="27">
-        <v>2.3335781081460154</v>
+        <v>2.1306079537211922</v>
       </c>
       <c r="J48" s="27">
-        <v>2.2167640241950699</v>
+        <v>2.0137938697702467</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1477866279398716</v>
+        <v>1.9448164735150482</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0760232157481169</v>
+        <v>1.8730530613232934</v>
       </c>
       <c r="M48" s="27">
-        <v>2.0113718047335691</v>
+        <v>1.8084016503087457</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9611172040494982</v>
+        <v>1.7581470496246747</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -59450,6 +59790,51 @@
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -59497,22 +59882,22 @@
     </row>
     <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -60424,40 +60809,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.208918035493463</v>
+        <v>2.0059478810686393</v>
       </c>
       <c r="C24" s="15">
-        <v>2.2089180443743959</v>
+        <v>2.0059478899495726</v>
       </c>
       <c r="D24" s="15">
-        <v>2.2089180085476507</v>
+        <v>2.0059478541228275</v>
       </c>
       <c r="E24" s="15">
-        <v>2.2089180171439557</v>
+        <v>2.0059478627191325</v>
       </c>
       <c r="F24" s="15">
-        <v>2.2089180274562565</v>
+        <v>2.0059478730314328</v>
       </c>
       <c r="G24" s="15">
-        <v>2.2089180286230832</v>
+        <v>2.0059478741982595</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2718885266136519</v>
+        <v>2.0689183721888282</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1440460770614469</v>
+        <v>1.9410759226366234</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0826875216639755</v>
+        <v>1.8797173672391521</v>
       </c>
       <c r="L24" s="27">
-        <v>2.0023953751351882</v>
+        <v>1.7994252207103647</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8797001402794935</v>
+        <v>1.67672998585467</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8144825697117761</v>
+        <v>1.6115124152869527</v>
       </c>
       <c r="Q24" s="28"/>
       <c r="R24" s="18"/>
@@ -60517,22 +60902,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -61407,40 +61792,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.3472323491829101</v>
+        <v>2.1442621947580864</v>
       </c>
       <c r="C48" s="15">
-        <v>2.3472323490799218</v>
+        <v>2.1442621946550986</v>
       </c>
       <c r="D48" s="15">
-        <v>2.3472323488495976</v>
+        <v>2.1442621944247744</v>
       </c>
       <c r="E48" s="15">
-        <v>2.3472323491831664</v>
+        <v>2.1442621947583431</v>
       </c>
       <c r="F48" s="15">
-        <v>2.3472323491344831</v>
+        <v>2.1442621947096594</v>
       </c>
       <c r="G48" s="15">
-        <v>2.3472323491832445</v>
+        <v>2.1442621947584213</v>
       </c>
       <c r="I48" s="27">
-        <v>2.3472323492958109</v>
+        <v>2.1442621948709872</v>
       </c>
       <c r="J48" s="27">
-        <v>2.2180673646194169</v>
+        <v>2.0150972101945932</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1458463528413265</v>
+        <v>1.9428761984165031</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0691968976365613</v>
+        <v>1.8662267432117379</v>
       </c>
       <c r="M48" s="27">
-        <v>1.9917833968801764</v>
+        <v>1.7888132424553529</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9248691808624778</v>
+        <v>1.7218990264376544</v>
       </c>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.15">
@@ -62724,7 +63109,7 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="27" style="8" bestFit="1" customWidth="1"/>
@@ -62751,22 +63136,22 @@
     </row>
     <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
@@ -63678,40 +64063,40 @@
         <v>29</v>
       </c>
       <c r="B24" s="15">
-        <v>2.1619203257699602</v>
+        <v>1.9589501713451367</v>
       </c>
       <c r="C24" s="15">
-        <v>2.1618639465083289</v>
+        <v>1.9588937920835054</v>
       </c>
       <c r="D24" s="15">
-        <v>2.1618701885910707</v>
+        <v>1.9589000341662473</v>
       </c>
       <c r="E24" s="15">
-        <v>2.1618972210068419</v>
+        <v>1.9589270665820184</v>
       </c>
       <c r="F24" s="15">
-        <v>2.1619186555679573</v>
+        <v>1.9589485011431338</v>
       </c>
       <c r="G24" s="15">
-        <v>2.1618967592061811</v>
+        <v>1.9589266047813576</v>
       </c>
       <c r="I24" s="27">
-        <v>2.2735213458055386</v>
+        <v>2.0705511913807149</v>
       </c>
       <c r="J24" s="27">
-        <v>2.1361753585250036</v>
+        <v>1.9332052041001802</v>
       </c>
       <c r="K24" s="27">
-        <v>2.0362433314048283</v>
+        <v>1.8332731769800048</v>
       </c>
       <c r="L24" s="27">
-        <v>1.9206142648483318</v>
+        <v>1.7176441104235083</v>
       </c>
       <c r="M24" s="27">
-        <v>1.8746475125038311</v>
+        <v>1.6716773580790076</v>
       </c>
       <c r="N24" s="27">
-        <v>1.8222742429849814</v>
+        <v>1.619304088560158</v>
       </c>
       <c r="Q24" s="28"/>
       <c r="R24" s="18"/>
@@ -63771,22 +64156,22 @@
     </row>
     <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12"/>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="I28" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
@@ -64661,40 +65046,40 @@
         <v>29</v>
       </c>
       <c r="B48" s="15">
-        <v>2.2935780200223368</v>
+        <v>2.0906078655975131</v>
       </c>
       <c r="C48" s="15">
-        <v>2.2935781106265067</v>
+        <v>2.0906079562016835</v>
       </c>
       <c r="D48" s="15">
-        <v>2.2935781106889417</v>
+        <v>2.090607956264118</v>
       </c>
       <c r="E48" s="15">
-        <v>2.2935153584728227</v>
+        <v>2.0905452040479995</v>
       </c>
       <c r="F48" s="15">
-        <v>2.2935781107040358</v>
+        <v>2.0906079562792126</v>
       </c>
       <c r="G48" s="15">
-        <v>2.2935781107004884</v>
+        <v>2.0906079562756652</v>
       </c>
       <c r="I48" s="27">
-        <v>2.2935781081460154</v>
+        <v>2.0906079537211921</v>
       </c>
       <c r="J48" s="27">
-        <v>2.1767640241950699</v>
+        <v>1.9737938697702464</v>
       </c>
       <c r="K48" s="27">
-        <v>2.1077866279398716</v>
+        <v>1.9048164735150481</v>
       </c>
       <c r="L48" s="27">
-        <v>2.0360232157481168</v>
+        <v>1.8330530613232934</v>
       </c>
       <c r="M48" s="27">
-        <v>1.9713718047335693</v>
+        <v>1.7684016503087459</v>
       </c>
       <c r="N48" s="27">
-        <v>1.9211172040494982</v>
+        <v>1.7181470496246747</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -64737,6 +65122,51 @@
       <c r="N49" s="26">
         <v>98.000000252691251</v>
       </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
